--- a/Lab 2 - Data generator/marketing_data_t1.xlsx
+++ b/Lab 2 - Data generator/marketing_data_t1.xlsx
@@ -476,47 +476,47 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>530.25</t>
+          <t>2055.13</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>6734</t>
+          <t>7515</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>13635</t>
+          <t>9977</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>152.64</t>
+          <t>464.32</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>74683</t>
+          <t>53446</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>377.61</t>
+          <t>1590.81</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2018-07-06</t>
+          <t>2018-02-27</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2018-08-23</t>
+          <t>2018-03-11</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>('SEO, Photos, SMS Marketing',)</t>
+          <t>('Email Marketing, Paid Ads, Video, Photos, SMS Marketing, Social Media',)</t>
         </is>
       </c>
     </row>
@@ -528,47 +528,47 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3635.59</t>
+          <t>2726.6800000000003</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4126</t>
+          <t>4989</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>28332</t>
+          <t>34036</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1043.54</t>
+          <t>513.26</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>74667</t>
+          <t>51342</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2592.05</t>
+          <t>2213.42</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2019-11-08</t>
+          <t>2015-05-16</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2019-12-28</t>
+          <t>2015-05-23</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>('Paid Ads, Content Marketing, Photos, Social Media',)</t>
+          <t>('Content Marketing, Paid Ads, SMS Marketing, Photos, Influencer Marketing',)</t>
         </is>
       </c>
     </row>
@@ -580,47 +580,47 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2739.21</t>
+          <t>877.87</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>9910</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>41583</t>
+          <t>16559</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2048.51</t>
+          <t>821.88</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>20769</t>
+          <t>5059</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>690.7</t>
+          <t>55.99</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2015-12-27</t>
+          <t>2017-10-22</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2016-02-20</t>
+          <t>2017-11-04</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>('SEO, Content Marketing, Video, Influencer Marketing, SMS Marketing',)</t>
+          <t>('Paid Ads, Email Marketing, Social Media, Content Marketing, Video, SEO',)</t>
         </is>
       </c>
     </row>
@@ -632,47 +632,47 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1281.65</t>
+          <t>2878.86</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5614</t>
+          <t>5868</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>17971</t>
+          <t>32036</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>453.03</t>
+          <t>1545.13</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>31102</t>
+          <t>50161</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>828.62</t>
+          <t>1333.73</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2018-07-04</t>
+          <t>2015-11-19</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2018-08-27</t>
+          <t>2015-11-29</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>('Paid Ads, Content Marketing, Photos',)</t>
+          <t>('SMS Marketing, Photos, Video, SEO, Email Marketing, Influencer Marketing',)</t>
         </is>
       </c>
     </row>
@@ -684,47 +684,47 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>339.61</t>
+          <t>708.27</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1206</t>
+          <t>7906</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1403</t>
+          <t>12717</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>60.41</t>
+          <t>617.52</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>5722</t>
+          <t>2101</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>279.2</t>
+          <t>90.75</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2016-10-07</t>
+          <t>2015-11-12</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2016-11-26</t>
+          <t>2015-11-20</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>('Video, Email Marketing, Influencer Marketing, Content Marketing, SEO',)</t>
+          <t>('Paid Ads, SEO, Video, SMS Marketing',)</t>
         </is>
       </c>
     </row>
@@ -736,47 +736,47 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1743.3500000000001</t>
+          <t>545.75</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>6242</t>
+          <t>9347</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>13420</t>
+          <t>12187</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>255.97</t>
+          <t>384.63</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>60645</t>
+          <t>70170</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1487.38</t>
+          <t>161.12</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2017-11-19</t>
+          <t>2015-12-10</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2018-01-12</t>
+          <t>2015-12-17</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>('Content Marketing, Social Media, SEO, Video, Photos, Email Marketing',)</t>
+          <t>('SMS Marketing, Paid Ads, Email Marketing',)</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1761.4899999999998</t>
+          <t>168.6</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>9137</t>
+          <t>9421</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>48055</t>
+          <t>7545</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>273.13</t>
+          <t>85.85</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>56545</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1488.36</t>
+          <t>82.75</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2015-10-10</t>
+          <t>2017-08-11</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2015-11-27</t>
+          <t>2017-08-26</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>('Paid Ads, SEO, Social Media, Email Marketing',)</t>
+          <t>('SEO, Influencer Marketing, Video, Social Media, Content Marketing',)</t>
         </is>
       </c>
     </row>
@@ -840,47 +840,47 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>900.14</t>
+          <t>826.07</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2822</t>
+          <t>5877</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8406</t>
+          <t>17599</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>344.24</t>
+          <t>525.34</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>59167</t>
+          <t>12115</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>555.9</t>
+          <t>300.73</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2015-11-19</t>
+          <t>2017-08-17</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2016-01-05</t>
+          <t>2017-08-28</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>('Social Media, Email Marketing, Influencer Marketing',)</t>
+          <t>('Social Media, Content Marketing, Video, SEO, Paid Ads',)</t>
         </is>
       </c>
     </row>
@@ -892,47 +892,47 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1289.1</t>
+          <t>647.76</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>8930</t>
+          <t>1676</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>29490</t>
+          <t>49951</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>370.39</t>
+          <t>538.06</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>18604</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>918.71</t>
+          <t>109.7</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2016-03-04</t>
+          <t>2019-12-09</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2016-04-28</t>
+          <t>2019-12-19</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>('Email Marketing, Video, SMS Marketing, Photos, Influencer Marketing, SEO',)</t>
+          <t>('SMS Marketing, Email Marketing, Photos',)</t>
         </is>
       </c>
     </row>
@@ -944,47 +944,47 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2067.47</t>
+          <t>3594.33</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>5795</t>
+          <t>4951</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>45057</t>
+          <t>8740</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2037.54</t>
+          <t>327.17</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>67095</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>29.93</t>
+          <t>3267.16</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2017-04-30</t>
+          <t>2018-02-11</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2017-06-19</t>
+          <t>2018-02-21</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>('SEO, Influencer Marketing, Social Media, Content Marketing, Email Marketing, Paid Ads',)</t>
+          <t>('Paid Ads, Content Marketing, Photos, Social Media',)</t>
         </is>
       </c>
     </row>
@@ -996,47 +996,47 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2389.0899999999997</t>
+          <t>1781.68</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>8722</t>
+          <t>3775</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>38319</t>
+          <t>35613</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>284.12</t>
+          <t>1700.74</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>60685</t>
+          <t>2643</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2104.97</t>
+          <t>80.94</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2017-01-03</t>
+          <t>2016-07-16</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2017-02-21</t>
+          <t>2016-07-29</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>('SMS Marketing, SEO, Video, Paid Ads',)</t>
+          <t>('SEO, Email Marketing, SMS Marketing, Influencer Marketing',)</t>
         </is>
       </c>
     </row>
@@ -1048,47 +1048,47 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1560.51</t>
+          <t>1139.48</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2203</t>
+          <t>2104</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>24493</t>
+          <t>30085</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>931.6</t>
+          <t>777.19</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>62513</t>
+          <t>24317</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>628.91</t>
+          <t>362.29</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2016-06-17</t>
+          <t>2015-01-26</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2016-08-06</t>
+          <t>2015-02-02</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>('SEO, Paid Ads, Photos, Email Marketing, Social Media, SMS Marketing',)</t>
+          <t>('Video, SMS Marketing, Influencer Marketing, Paid Ads, Social Media',)</t>
         </is>
       </c>
     </row>
@@ -1100,47 +1100,47 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1790.74</t>
+          <t>2331.67</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>7071</t>
+          <t>9813</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>38100</t>
+          <t>3373</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1636.33</t>
+          <t>124.4</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>14169</t>
+          <t>63708</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>154.41</t>
+          <t>2207.27</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2016-11-03</t>
+          <t>2019-01-16</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2016-12-25</t>
+          <t>2019-01-27</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>('SMS Marketing, Paid Ads, Social Media, Influencer Marketing',)</t>
+          <t>('Influencer Marketing, SMS Marketing, Social Media',)</t>
         </is>
       </c>
     </row>
@@ -1152,47 +1152,47 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>161.34</t>
+          <t>893.0500000000001</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>5129</t>
+          <t>9004</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>4370</t>
+          <t>35705</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>61.43</t>
+          <t>859.22</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>7750</t>
+          <t>12723</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>99.91</t>
+          <t>33.83</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2018-04-11</t>
+          <t>2018-06-15</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2018-06-03</t>
+          <t>2018-06-21</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>('Social Media, Content Marketing, SEO, SMS Marketing',)</t>
+          <t>('Video, Email Marketing, SMS Marketing, Social Media, Influencer Marketing, Photos',)</t>
         </is>
       </c>
     </row>
@@ -1204,47 +1204,47 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1419.03</t>
+          <t>1173.73</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>8481</t>
+          <t>4725</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>16210</t>
+          <t>26839</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>680.72</t>
+          <t>737.87</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>29485</t>
+          <t>20149</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>738.31</t>
+          <t>435.86</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2018-09-16</t>
+          <t>2018-06-14</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2018-11-05</t>
+          <t>2018-06-27</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>('Influencer Marketing, Photos, Content Marketing',)</t>
+          <t>('SMS Marketing, Content Marketing, Photos, Influencer Marketing',)</t>
         </is>
       </c>
     </row>
@@ -1256,47 +1256,47 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1925.98</t>
+          <t>2704.87</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>7645</t>
+          <t>9846</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>43660</t>
+          <t>27664</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>972.65</t>
+          <t>363.95</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>23952</t>
+          <t>64816</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>953.33</t>
+          <t>2340.92</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2016-09-12</t>
+          <t>2016-10-29</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2016-11-04</t>
+          <t>2016-11-09</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>('Email Marketing, Video, Paid Ads, SMS Marketing, SEO, Influencer Marketing',)</t>
+          <t>('SMS Marketing, Social Media, Influencer Marketing, SEO',)</t>
         </is>
       </c>
     </row>
@@ -1308,47 +1308,47 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>3801.7799999999997</t>
+          <t>1620.39</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>3986</t>
+          <t>8187</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>45890</t>
+          <t>42919</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2141.62</t>
+          <t>1583.73</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>46438</t>
+          <t>1587</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1660.16</t>
+          <t>36.66</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2016-09-25</t>
+          <t>2015-10-12</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2016-11-17</t>
+          <t>2015-10-27</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>('SEO, Paid Ads, Email Marketing, SMS Marketing, Social Media',)</t>
+          <t>('Social Media, Influencer Marketing, SEO, Email Marketing, Photos, Content Marketing',)</t>
         </is>
       </c>
     </row>
@@ -1360,47 +1360,47 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1468.38</t>
+          <t>3907.24</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>9082</t>
+          <t>1105</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>26109</t>
+          <t>41427</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>787.23</t>
+          <t>359.52</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>30348</t>
+          <t>72118</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>681.15</t>
+          <t>3547.72</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2015-02-08</t>
+          <t>2018-07-24</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2015-04-01</t>
+          <t>2018-07-31</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>('Social Media, Photos, SEO, Video, Paid Ads, Email Marketing',)</t>
+          <t>('SEO, Influencer Marketing, Social Media, Content Marketing, Email Marketing, Paid Ads',)</t>
         </is>
       </c>
     </row>
@@ -1412,47 +1412,47 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2617.4500000000003</t>
+          <t>2389.0899999999997</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>3485</t>
+          <t>8722</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>6421</t>
+          <t>38319</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>134.88</t>
+          <t>284.12</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61893</t>
+          <t>60685</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2482.57</t>
+          <t>2104.97</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2019-06-12</t>
+          <t>2017-04-09</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2019-08-07</t>
+          <t>2017-04-17</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>('Social Media, Photos, Email Marketing',)</t>
+          <t>('SMS Marketing, SEO, Video, Paid Ads',)</t>
         </is>
       </c>
     </row>
@@ -1464,47 +1464,47 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>814.99</t>
+          <t>2911.1299999999997</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1766</t>
+          <t>6775</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>20210</t>
+          <t>13422</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>627.81</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>73969</t>
+          <t>60520</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>187.18</t>
+          <t>2830.43</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2017-05-23</t>
+          <t>2019-02-20</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2017-07-17</t>
+          <t>2019-03-01</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>('Influencer Marketing, Social Media, SEO',)</t>
+          <t>('Paid Ads, SEO, Email Marketing, Photos, Influencer Marketing',)</t>
         </is>
       </c>
     </row>
@@ -1516,37 +1516,37 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2568.23</t>
+          <t>1475.24</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>7684</t>
+          <t>6428</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>22839</t>
+          <t>20397</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>671.65</t>
+          <t>470.3</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>42047</t>
+          <t>67151</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1896.58</t>
+          <t>1004.94</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2018-07-27</t>
+          <t>2018-09-06</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>('Photos, Paid Ads, Social Media, Influencer Marketing',)</t>
+          <t>('Influencer Marketing, Email Marketing, Social Media, SEO',)</t>
         </is>
       </c>
     </row>
@@ -1568,47 +1568,47 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2113.11</t>
+          <t>1700.95</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>5711</t>
+          <t>7998</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>39130</t>
+          <t>25809</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1738.51</t>
+          <t>1088.74</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>47965</t>
+          <t>35694</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>374.6</t>
+          <t>612.21</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2016-10-31</t>
+          <t>2019-03-14</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2016-12-18</t>
+          <t>2019-03-24</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>('Photos, Content Marketing, Video, Paid Ads',)</t>
+          <t>('SMS Marketing, Video, Influencer Marketing, Content Marketing, Photos, Social Media',)</t>
         </is>
       </c>
     </row>
@@ -1620,47 +1620,47 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1488.68</t>
+          <t>2718.3199999999997</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1775</t>
+          <t>9811</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>11148</t>
+          <t>47220</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>282.02</t>
+          <t>1990.12</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>51175</t>
+          <t>16252</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1206.66</t>
+          <t>728.2</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2019-05-06</t>
+          <t>2018-03-19</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2019-06-28</t>
+          <t>2018-03-30</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>('Content Marketing, Paid Ads, Email Marketing',)</t>
+          <t>('SEO, Video, Content Marketing, Influencer Marketing, Paid Ads',)</t>
         </is>
       </c>
     </row>
@@ -1672,47 +1672,47 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1217.07</t>
+          <t>1319.73</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>9158</t>
+          <t>4537</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8042</t>
+          <t>25491</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>184.83</t>
+          <t>544.17</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>65588</t>
+          <t>26610</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1032.24</t>
+          <t>775.56</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2015-11-14</t>
+          <t>2016-03-28</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2016-01-07</t>
+          <t>2016-04-12</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>('Video, Influencer Marketing, Content Marketing, SEO',)</t>
+          <t>('Video, SEO, Social Media, Content Marketing',)</t>
         </is>
       </c>
     </row>
@@ -1724,47 +1724,47 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>3162.13</t>
+          <t>1226.38</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>4619</t>
+          <t>5467</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>40931</t>
+          <t>8406</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1574.9</t>
+          <t>265.74</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>67857</t>
+          <t>30583</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1587.23</t>
+          <t>960.64</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2018-02-03</t>
+          <t>2018-08-27</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2018-03-27</t>
+          <t>2018-09-11</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>('Influencer Marketing, Content Marketing, Social Media',)</t>
+          <t>('Influencer Marketing, Video, Content Marketing',)</t>
         </is>
       </c>
     </row>
@@ -1776,47 +1776,47 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>662.63</t>
+          <t>3801.7799999999997</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>4312</t>
+          <t>3986</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>38563</t>
+          <t>45890</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>616.05</t>
+          <t>2141.62</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1831</t>
+          <t>46438</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>46.58</t>
+          <t>1660.16</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2017-11-01</t>
+          <t>2016-10-03</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2017-12-22</t>
+          <t>2016-10-15</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>('Content Marketing, Social Media, Paid Ads',)</t>
+          <t>('SEO, Paid Ads, Email Marketing, SMS Marketing, Social Media',)</t>
         </is>
       </c>
     </row>
@@ -1828,47 +1828,47 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1955.2400000000002</t>
+          <t>1468.38</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>6889</t>
+          <t>9082</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>24393</t>
+          <t>26109</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>918.08</t>
+          <t>787.23</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>25826</t>
+          <t>30348</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1037.16</t>
+          <t>681.15</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2017-02-22</t>
+          <t>2018-08-13</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2017-04-15</t>
+          <t>2018-08-24</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>('Paid Ads, Social Media, Influencer Marketing',)</t>
+          <t>('Social Media, Photos, SEO, Video, Paid Ads, Email Marketing',)</t>
         </is>
       </c>
     </row>
@@ -1880,47 +1880,47 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1774.98</t>
+          <t>2617.4500000000003</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>9989</t>
+          <t>3485</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>30389</t>
+          <t>6421</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1486.85</t>
+          <t>134.88</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>13014</t>
+          <t>61893</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>288.13</t>
+          <t>2482.57</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2019-05-05</t>
+          <t>2016-08-20</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2019-06-23</t>
+          <t>2016-09-04</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>('Social Media, Influencer Marketing, Email Marketing, Photos, SMS Marketing, Paid Ads',)</t>
+          <t>('Social Media, Photos, Email Marketing',)</t>
         </is>
       </c>
     </row>
@@ -1932,47 +1932,47 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1023.8299999999999</t>
+          <t>814.99</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>9481</t>
+          <t>1766</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>12670</t>
+          <t>20210</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>255.91</t>
+          <t>627.81</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>47489</t>
+          <t>73969</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>767.92</t>
+          <t>187.18</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2016-12-27</t>
+          <t>2017-04-13</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2017-02-17</t>
+          <t>2017-04-27</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>('SMS Marketing, Photos, Email Marketing, Influencer Marketing',)</t>
+          <t>('Influencer Marketing, Social Media, SEO',)</t>
         </is>
       </c>
     </row>
@@ -1984,47 +1984,47 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1034.75</t>
+          <t>2384.1499999999996</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>5867</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>45332</t>
+          <t>42005</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>825.88</t>
+          <t>1870.35</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>20515</t>
+          <t>10914</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>208.87</t>
+          <t>513.8</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2019-04-01</t>
+          <t>2015-08-12</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2019-05-21</t>
+          <t>2015-08-24</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>('Video, Email Marketing, Photos',)</t>
+          <t>('Photos, Paid Ads, Social Media, Influencer Marketing',)</t>
         </is>
       </c>
     </row>
@@ -2036,47 +2036,47 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2776.21</t>
+          <t>2113.11</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>7198</t>
+          <t>5711</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>21569</t>
+          <t>39130</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>412.79</t>
+          <t>1738.51</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>50532</t>
+          <t>47965</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2363.42</t>
+          <t>374.6</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2019-12-08</t>
+          <t>2016-03-02</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2020-01-25</t>
+          <t>2016-03-09</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>('Photos, Video, Social Media',)</t>
+          <t>('Photos, Content Marketing, Video, Paid Ads',)</t>
         </is>
       </c>
     </row>
@@ -2088,47 +2088,47 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2355.19</t>
+          <t>1488.68</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>3780</t>
+          <t>1775</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>45055</t>
+          <t>11148</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1954.21</t>
+          <t>282.02</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>36134</t>
+          <t>51175</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>400.98</t>
+          <t>1206.66</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2016-10-23</t>
+          <t>2018-12-18</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2016-12-15</t>
+          <t>2018-12-30</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>('Photos, Video, Influencer Marketing',)</t>
+          <t>('Content Marketing, Paid Ads, Email Marketing',)</t>
         </is>
       </c>
     </row>
@@ -2140,47 +2140,47 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>420.35</t>
+          <t>1217.07</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>9110</t>
+          <t>9158</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>12511</t>
+          <t>8042</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>85.78</t>
+          <t>184.83</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>7170</t>
+          <t>65588</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>334.57</t>
+          <t>1032.24</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2019-10-27</t>
+          <t>2017-09-27</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2019-12-20</t>
+          <t>2017-10-10</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>('Social Media, Email Marketing, SMS Marketing, Influencer Marketing, Photos, SEO',)</t>
+          <t>('Video, Influencer Marketing, Content Marketing, SEO',)</t>
         </is>
       </c>
     </row>
@@ -2192,47 +2192,47 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>685.59</t>
+          <t>1864.81</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>5464</t>
+          <t>9445</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>15871</t>
+          <t>43599</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>603.88</t>
+          <t>1153.77</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>20356</t>
+          <t>44365</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>81.71</t>
+          <t>711.04</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2015-06-11</t>
+          <t>2018-02-04</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2015-07-29</t>
+          <t>2018-02-10</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>('Email Marketing, Video, Social Media, SEO',)</t>
+          <t>('Email Marketing, Video, Content Marketing, SMS Marketing, Social Media',)</t>
         </is>
       </c>
     </row>
@@ -2244,47 +2244,47 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1918.32</t>
+          <t>1797.1</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1734</t>
+          <t>1999</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>36291</t>
+          <t>22325</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1190.62</t>
+          <t>733.49</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>51847</t>
+          <t>40936</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>727.7</t>
+          <t>1063.61</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2019-10-29</t>
+          <t>2017-06-25</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2019-12-19</t>
+          <t>2017-07-10</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>('Social Media, Email Marketing, Content Marketing',)</t>
+          <t>('Video, Content Marketing, Photos, Social Media, Paid Ads',)</t>
         </is>
       </c>
     </row>
@@ -2296,47 +2296,47 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2808.84</t>
+          <t>1955.2400000000002</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>5530</t>
+          <t>6889</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>47529</t>
+          <t>24393</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1670.24</t>
+          <t>918.08</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>34252</t>
+          <t>25826</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1138.6</t>
+          <t>1037.16</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2015-12-05</t>
+          <t>2018-11-01</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2016-01-26</t>
+          <t>2018-11-12</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>('Email Marketing, Photos, Social Media, SMS Marketing, Influencer Marketing',)</t>
+          <t>('Paid Ads, Social Media, Influencer Marketing',)</t>
         </is>
       </c>
     </row>
@@ -2348,47 +2348,47 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1260.6599999999999</t>
+          <t>3976.51</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1589</t>
+          <t>9223</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>19403</t>
+          <t>35652</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>930.14</t>
+          <t>1780.68</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>68137</t>
+          <t>44987</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>330.52</t>
+          <t>2195.83</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2017-04-05</t>
+          <t>2017-12-04</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2017-05-24</t>
+          <t>2017-12-12</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>('Influencer Marketing, SEO, Content Marketing, Paid Ads',)</t>
+          <t>('Content Marketing, Influencer Marketing, SEO, SMS Marketing, Photos',)</t>
         </is>
       </c>
     </row>
@@ -2400,47 +2400,47 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1364.34</t>
+          <t>4277.9</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>9768</t>
+          <t>2902</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>19432</t>
+          <t>48166</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>141.99</t>
+          <t>1403.59</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>62486</t>
+          <t>64942</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1222.35</t>
+          <t>2874.31</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2018-09-07</t>
+          <t>2017-02-05</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2018-10-25</t>
+          <t>2017-02-16</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>('SMS Marketing, Social Media, Content Marketing, Video',)</t>
+          <t>('Social Media, Content Marketing, Photos, Influencer Marketing, SMS Marketing',)</t>
         </is>
       </c>
     </row>
@@ -2452,47 +2452,47 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1022.22</t>
+          <t>2729.98</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>9908</t>
+          <t>5318</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>5781</t>
+          <t>34900</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>133.51</t>
+          <t>1117.31</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>38009</t>
+          <t>45396</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>888.71</t>
+          <t>1612.67</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2015-11-15</t>
+          <t>2016-05-20</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2016-01-06</t>
+          <t>2016-05-27</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>('Email Marketing, SMS Marketing, Photos',)</t>
+          <t>('Email Marketing, SEO, SMS Marketing, Social Media, Paid Ads, Photos',)</t>
         </is>
       </c>
     </row>
@@ -2504,47 +2504,47 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>458.15</t>
+          <t>551.1</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>5731</t>
+          <t>9609</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>11706</t>
+          <t>30592</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>106.39</t>
+          <t>378.12</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>69354</t>
+          <t>41796</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>351.76</t>
+          <t>172.98</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2015-04-28</t>
+          <t>2018-12-06</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2015-06-20</t>
+          <t>2018-12-15</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>('Influencer Marketing, SEO, Content Marketing, Email Marketing, Paid Ads, Video',)</t>
+          <t>('Influencer Marketing, Content Marketing, SMS Marketing, Paid Ads, Email Marketing, Video',)</t>
         </is>
       </c>
     </row>
@@ -2556,47 +2556,47 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>389.98</t>
+          <t>3412.5</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>4965</t>
+          <t>6535</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>26379</t>
+          <t>28380</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>383.6</t>
+          <t>536.37</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>67432</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>6.38</t>
+          <t>2876.13</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2015-11-09</t>
+          <t>2016-02-03</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2016-01-02</t>
+          <t>2016-02-12</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>('SEO, Influencer Marketing, Social Media, Content Marketing, Paid Ads',)</t>
+          <t>('Photos, SMS Marketing, Influencer Marketing, Content Marketing',)</t>
         </is>
       </c>
     </row>
@@ -2608,47 +2608,47 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>374.16999999999996</t>
+          <t>2303.61</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>3071</t>
+          <t>8350</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>7669</t>
+          <t>49737</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>356.34</t>
+          <t>2265.56</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>18013</t>
+          <t>17627</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>17.83</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2017-10-17</t>
+          <t>2017-11-22</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2017-12-09</t>
+          <t>2017-12-03</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>('Social Media, Photos, SEO, SMS Marketing, Content Marketing',)</t>
+          <t>('Influencer Marketing, Social Media, SMS Marketing',)</t>
         </is>
       </c>
     </row>
@@ -2660,47 +2660,47 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2364.81</t>
+          <t>610.96</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2802</t>
+          <t>3500</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>15464</t>
+          <t>8779</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>562.57</t>
+          <t>116.47</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>48830</t>
+          <t>71339</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1802.24</t>
+          <t>494.49</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2017-10-26</t>
+          <t>2016-11-12</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2017-12-20</t>
+          <t>2016-11-23</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>('Paid Ads, Photos, Social Media, Content Marketing',)</t>
+          <t>('SEO, Social Media, Content Marketing, SMS Marketing, Paid Ads, Photos',)</t>
         </is>
       </c>
     </row>
@@ -2712,47 +2712,47 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>466.64</t>
+          <t>284.03000000000003</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2398</t>
+          <t>8833</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>8282</t>
+          <t>1843</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>254.82</t>
+          <t>53.82</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>19873</t>
+          <t>35986</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>211.82</t>
+          <t>230.21</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2015-12-23</t>
+          <t>2019-03-28</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2016-02-15</t>
+          <t>2019-04-06</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>('SMS Marketing, Influencer Marketing, Photos, Video, Social Media, Email Marketing',)</t>
+          <t>('SEO, Email Marketing, Video',)</t>
         </is>
       </c>
     </row>
@@ -2764,47 +2764,47 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2312.2599999999998</t>
+          <t>2030.33</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>5448</t>
+          <t>4764</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>26501</t>
+          <t>8128</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>168.41</t>
+          <t>237.62</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>53301</t>
+          <t>37754</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2143.85</t>
+          <t>1792.71</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2017-05-30</t>
+          <t>2016-04-27</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2017-07-18</t>
+          <t>2016-05-08</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>('SEO, Influencer Marketing, Photos, Paid Ads, Video',)</t>
+          <t>('Content Marketing, Paid Ads, Photos, SMS Marketing, Social Media, Influencer Marketing',)</t>
         </is>
       </c>
     </row>
@@ -2816,47 +2816,47 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>677.3</t>
+          <t>1567.3</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1118</t>
+          <t>2961</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>8034</t>
+          <t>28066</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>257.48</t>
+          <t>223.03</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>57521</t>
+          <t>28174</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>419.82</t>
+          <t>1344.27</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2015-11-03</t>
+          <t>2015-11-01</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2015-12-25</t>
+          <t>2015-11-13</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>('Photos, SMS Marketing, Social Media, Video',)</t>
+          <t>('Paid Ads, Social Media, Email Marketing, SMS Marketing',)</t>
         </is>
       </c>
     </row>
@@ -2868,47 +2868,47 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1170.62</t>
+          <t>1108.83</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2272</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>48977</t>
+          <t>22584</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>374.07</t>
+          <t>445.3</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>24971</t>
+          <t>38395</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>796.55</t>
+          <t>663.53</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2017-01-19</t>
+          <t>2019-07-28</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2017-03-15</t>
+          <t>2019-08-05</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>('Email Marketing, SMS Marketing, Influencer Marketing, Video, SEO',)</t>
+          <t>('SMS Marketing, Social Media, Content Marketing, Video',)</t>
         </is>
       </c>
     </row>
@@ -2920,47 +2920,47 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>3225.46</t>
+          <t>428.23</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>7887</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>21621</t>
+          <t>20180</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>613.33</t>
+          <t>180.56</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>73438</t>
+          <t>40153</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2612.13</t>
+          <t>247.67</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2017-08-02</t>
+          <t>2019-12-30</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2017-09-17</t>
+          <t>2020-01-05</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>('Email Marketing, SEO, Video, SMS Marketing, Social Media, Photos',)</t>
+          <t>('Video, Email Marketing, Photos, Influencer Marketing',)</t>
         </is>
       </c>
     </row>
@@ -2972,47 +2972,47 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>3042.45</t>
+          <t>908.81</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>1236</t>
+          <t>2914</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>48336</t>
+          <t>10737</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1214.61</t>
+          <t>291.3</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>47369</t>
+          <t>14368</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>1827.84</t>
+          <t>617.51</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2019-11-11</t>
+          <t>2018-10-16</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2019-12-29</t>
+          <t>2018-10-27</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>('SMS Marketing, Email Marketing, Photos, Video, Social Media, Content Marketing',)</t>
+          <t>('SMS Marketing, Influencer Marketing, SEO, Email Marketing',)</t>
         </is>
       </c>
     </row>
@@ -3024,47 +3024,47 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1552.72</t>
+          <t>3723.8199999999997</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>3383</t>
+          <t>6673</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>20804</t>
+          <t>39645</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>673.85</t>
+          <t>824.05</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>20117</t>
+          <t>73521</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>878.87</t>
+          <t>2899.77</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2015-07-24</t>
+          <t>2017-09-18</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2015-09-16</t>
+          <t>2017-10-01</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>('Content Marketing, SEO, SMS Marketing, Influencer Marketing',)</t>
+          <t>('Paid Ads, Email Marketing, SEO, Content Marketing',)</t>
         </is>
       </c>
     </row>
@@ -3076,47 +3076,47 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1025.3</t>
+          <t>1647.58</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>3974</t>
+          <t>6438</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>39189</t>
+          <t>41961</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>420.82</t>
+          <t>757.43</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>48077</t>
+          <t>24685</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>604.48</t>
+          <t>890.15</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2015-10-31</t>
+          <t>2016-06-28</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2015-12-17</t>
+          <t>2016-07-07</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>('Social Media, Content Marketing, Email Marketing, Influencer Marketing, Paid Ads, SMS Marketing',)</t>
+          <t>('Photos, Paid Ads, Social Media',)</t>
         </is>
       </c>
     </row>
@@ -3128,47 +3128,47 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>446.87</t>
+          <t>623.9799999999999</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>6891</t>
+          <t>9293</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>12635</t>
+          <t>12763</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>425.4</t>
+          <t>74.05</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>7256</t>
+          <t>21226</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>549.93</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2018-05-03</t>
+          <t>2015-10-02</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2018-06-25</t>
+          <t>2015-10-10</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>('SEO, Photos, SMS Marketing, Content Marketing, Social Media',)</t>
+          <t>('Photos, Content Marketing, Social Media, Paid Ads',)</t>
         </is>
       </c>
     </row>
@@ -3180,47 +3180,47 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1394.92</t>
+          <t>1470.44</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>5071</t>
+          <t>7276</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>10721</t>
+          <t>32900</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>234.27</t>
+          <t>1256.58</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>50212</t>
+          <t>29613</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>1160.65</t>
+          <t>213.86</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2019-02-03</t>
+          <t>2017-09-10</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2019-03-27</t>
+          <t>2017-09-21</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>('Influencer Marketing, Video, Paid Ads, SMS Marketing, Content Marketing, Social Media',)</t>
+          <t>('SMS Marketing, Email Marketing, Influencer Marketing, SEO',)</t>
         </is>
       </c>
     </row>
@@ -3232,47 +3232,47 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1967.9099999999999</t>
+          <t>1017.63</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>1921</t>
+          <t>3384</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>31209</t>
+          <t>11368</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1195.99</t>
+          <t>538.62</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>18445</t>
+          <t>10456</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>771.92</t>
+          <t>479.01</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2016-04-11</t>
+          <t>2016-05-24</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2016-06-02</t>
+          <t>2016-05-31</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>('Social Media, SMS Marketing, Email Marketing, Paid Ads, Photos, Influencer Marketing',)</t>
+          <t>('Video, SEO, Influencer Marketing, Email Marketing',)</t>
         </is>
       </c>
     </row>
@@ -3284,47 +3284,47 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>766.9499999999999</t>
+          <t>2312.2599999999998</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>1904</t>
+          <t>5448</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>5060</t>
+          <t>26501</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>200.29</t>
+          <t>168.41</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>15657</t>
+          <t>53301</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>566.66</t>
+          <t>2143.85</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2017-10-06</t>
+          <t>2017-04-27</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2017-11-24</t>
+          <t>2017-05-05</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>('Social Media, Influencer Marketing, Content Marketing, Video, SEO',)</t>
+          <t>('SEO, Influencer Marketing, Photos, Paid Ads, Video',)</t>
         </is>
       </c>
     </row>
@@ -3336,47 +3336,47 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>4006.4800000000005</t>
+          <t>501.91</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>5256</t>
+          <t>6852</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>42793</t>
+          <t>31774</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1634.16</t>
+          <t>177.68</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>66045</t>
+          <t>10774</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2372.32</t>
+          <t>324.23</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2016-12-02</t>
+          <t>2018-01-12</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2017-01-21</t>
+          <t>2018-01-25</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>('Social Media, SMS Marketing, Photos, Email Marketing, Paid Ads',)</t>
+          <t>('Photos, SMS Marketing, Social Media, Video',)</t>
         </is>
       </c>
     </row>
@@ -3388,47 +3388,47 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2258.94</t>
+          <t>627.76</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>7080</t>
+          <t>9928</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>35704</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>19.46</t>
+          <t>405.64</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>54694</t>
+          <t>73435</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2239.48</t>
+          <t>222.12</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2016-02-11</t>
+          <t>2015-12-31</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2016-04-04</t>
+          <t>2016-01-10</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>('Content Marketing, Social Media, Video, Email Marketing, SMS Marketing, SEO',)</t>
+          <t>('Influencer Marketing, Video, Social Media, Content Marketing, Photos, SEO',)</t>
         </is>
       </c>
     </row>
@@ -3440,47 +3440,47 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>3592.56</t>
+          <t>1950.24</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>1613</t>
+          <t>2917</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>49609</t>
+          <t>16664</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1720.75</t>
+          <t>739.26</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>53935</t>
+          <t>57394</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>1871.81</t>
+          <t>1210.98</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2017-01-12</t>
+          <t>2015-12-19</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2017-03-01</t>
+          <t>2015-12-24</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>('Email Marketing, Photos, SMS Marketing, Video, SEO',)</t>
+          <t>('Content Marketing, Influencer Marketing, Photos, Social Media',)</t>
         </is>
       </c>
     </row>
@@ -3492,47 +3492,47 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>3050.17</t>
+          <t>358.73</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>6550</t>
+          <t>3356</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>41757</t>
+          <t>38973</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1837.84</t>
+          <t>343.38</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>57724</t>
+          <t>10880</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>1212.33</t>
+          <t>15.35</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2016-03-07</t>
+          <t>2018-03-26</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2016-04-22</t>
+          <t>2018-04-01</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>('Photos, Video, Paid Ads, Social Media, Email Marketing',)</t>
+          <t>('SEO, Influencer Marketing, Email Marketing',)</t>
         </is>
       </c>
     </row>
@@ -3544,47 +3544,47 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1524.28</t>
+          <t>2207.09</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>6651</t>
+          <t>3401</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>32125</t>
+          <t>42149</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1134.03</t>
+          <t>1553.53</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>11559</t>
+          <t>14846</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>390.25</t>
+          <t>653.56</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2015-05-06</t>
+          <t>2017-09-29</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>2015-06-24</t>
+          <t>2017-10-05</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>('Paid Ads, Content Marketing, Social Media, Email Marketing, SEO',)</t>
+          <t>('Social Media, Paid Ads, SMS Marketing, Photos, Video, Content Marketing',)</t>
         </is>
       </c>
     </row>
@@ -3596,47 +3596,47 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1727.61</t>
+          <t>1679.46</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>3793</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>34404</t>
+          <t>16197</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1705.08</t>
+          <t>534.36</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>17336</t>
+          <t>69031</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>22.53</t>
+          <t>1145.1</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2019-11-09</t>
+          <t>2017-10-16</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>2020-01-01</t>
+          <t>2017-10-30</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>('Paid Ads, Photos, Influencer Marketing, Video',)</t>
+          <t>('Content Marketing, Paid Ads, Email Marketing, Photos',)</t>
         </is>
       </c>
     </row>
@@ -3648,47 +3648,47 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2997.33</t>
+          <t>1650.92</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>49392</t>
+          <t>49336</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2287.8</t>
+          <t>1484.7</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>32800</t>
+          <t>33968</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>709.53</t>
+          <t>166.22</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2015-06-20</t>
+          <t>2017-08-23</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2015-08-08</t>
+          <t>2017-08-30</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>('SEO, Video, Photos, Email Marketing, Influencer Marketing, Paid Ads',)</t>
+          <t>('Email Marketing, Influencer Marketing, Content Marketing, Paid Ads, Video, SMS Marketing',)</t>
         </is>
       </c>
     </row>
@@ -3700,47 +3700,47 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>704.45</t>
+          <t>1006.11</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>4521</t>
+          <t>5742</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>29713</t>
+          <t>28337</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>505.83</t>
+          <t>1005.96</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>57011</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>198.62</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2018-12-27</t>
+          <t>2017-11-02</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2019-02-15</t>
+          <t>2017-11-12</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>('Paid Ads, SEO, SMS Marketing, Photos',)</t>
+          <t>('Paid Ads, Email Marketing, Photos, Social Media, SEO',)</t>
         </is>
       </c>
     </row>
@@ -3752,47 +3752,47 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>123.07</t>
+          <t>371.99</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>4320</t>
+          <t>1929</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>15435</t>
+          <t>6250</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>117.46</t>
+          <t>235.08</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>23442</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>136.91</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2019-01-23</t>
+          <t>2015-01-07</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>2019-03-16</t>
+          <t>2015-01-20</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>('Photos, Social Media, Video, Content Marketing, SEO, SMS Marketing',)</t>
+          <t>('SMS Marketing, SEO, Content Marketing',)</t>
         </is>
       </c>
     </row>
@@ -3804,47 +3804,47 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>302.17</t>
+          <t>1021.1500000000001</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2816</t>
+          <t>2491</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>5906</t>
+          <t>13634</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>159.02</t>
+          <t>577.07</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>6032</t>
+          <t>12594</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>143.15</t>
+          <t>444.08</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2019-08-29</t>
+          <t>2016-08-13</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>2019-10-15</t>
+          <t>2016-08-26</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>('SMS Marketing, Photos, Paid Ads, Social Media',)</t>
+          <t>('Video, Photos, SMS Marketing, Social Media, Influencer Marketing, Email Marketing',)</t>
         </is>
       </c>
     </row>
@@ -3856,47 +3856,47 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1385.3300000000002</t>
+          <t>587.6</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>7574</t>
+          <t>5542</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>28099</t>
+          <t>42010</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>259.68</t>
+          <t>562.76</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>59341</t>
+          <t>47988</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>1125.65</t>
+          <t>24.84</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2019-09-13</t>
+          <t>2017-07-30</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>2019-10-30</t>
+          <t>2017-08-10</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>('SMS Marketing, Influencer Marketing, Social Media, Photos, SEO',)</t>
+          <t>('Content Marketing, SMS Marketing, Email Marketing, Paid Ads, Influencer Marketing',)</t>
         </is>
       </c>
     </row>
@@ -3908,47 +3908,47 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>154.47</t>
+          <t>1207.17</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>9481</t>
+          <t>2679</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>25765</t>
+          <t>11890</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>153.13</t>
+          <t>306.79</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>48204</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>900.38</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2017-01-03</t>
+          <t>2016-08-05</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>2017-02-23</t>
+          <t>2016-08-14</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>('Social Media, Photos, Influencer Marketing, Email Marketing',)</t>
+          <t>('Video, Photos, Email Marketing, Content Marketing',)</t>
         </is>
       </c>
     </row>
@@ -3960,47 +3960,47 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1316.74</t>
+          <t>908.4100000000001</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>8850</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>9437</t>
+          <t>28034</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>325.99</t>
+          <t>181.7</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>60994</t>
+          <t>31052</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>990.75</t>
+          <t>726.71</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2018-08-14</t>
+          <t>2016-06-13</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>2018-10-06</t>
+          <t>2016-06-22</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>('Social Media, SEO, SMS Marketing, Photos, Video, Content Marketing',)</t>
+          <t>('Email Marketing, SMS Marketing, Video',)</t>
         </is>
       </c>
     </row>
@@ -4012,47 +4012,47 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1479.6200000000001</t>
+          <t>1252.38</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>6016</t>
+          <t>7046</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>28144</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>51.21</t>
+          <t>917.63</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>29562</t>
+          <t>15598</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>1428.41</t>
+          <t>334.75</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2017-02-09</t>
+          <t>2019-10-02</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>2017-03-28</t>
+          <t>2019-10-08</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>('Social Media, SEO, Video, Content Marketing, SMS Marketing',)</t>
+          <t>('Video, Email Marketing, SEO, Social Media, Paid Ads',)</t>
         </is>
       </c>
     </row>
@@ -4064,47 +4064,47 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>4610.04</t>
+          <t>2563.37</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>3041</t>
+          <t>4115</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>49435</t>
+          <t>32524</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2320.67</t>
+          <t>720.19</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>64558</t>
+          <t>48378</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2289.37</t>
+          <t>1843.18</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2016-11-08</t>
+          <t>2016-05-10</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>2016-12-28</t>
+          <t>2016-05-21</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>('Social Media, Paid Ads, Photos',)</t>
+          <t>('Influencer Marketing, Video, Content Marketing, Email Marketing, Social Media, SMS Marketing',)</t>
         </is>
       </c>
     </row>
@@ -4116,47 +4116,47 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1179.61</t>
+          <t>4398.530000000001</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>3322</t>
+          <t>9275</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>44814</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>79.86</t>
+          <t>1771.4</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>24712</t>
+          <t>72740</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>1099.75</t>
+          <t>2627.13</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2015-10-31</t>
+          <t>2019-01-18</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2015-12-18</t>
+          <t>2019-01-25</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>('Video, Email Marketing, Paid Ads, SEO',)</t>
+          <t>('SEO, Influencer Marketing, Paid Ads, SMS Marketing, Photos',)</t>
         </is>
       </c>
     </row>
@@ -4168,47 +4168,47 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>1556.31</t>
+          <t>793.3000000000001</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2053</t>
+          <t>7135</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>39807</t>
+          <t>49521</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>949.22</t>
+          <t>762.46</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>13961</t>
+          <t>1813</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>607.09</t>
+          <t>30.84</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2017-10-30</t>
+          <t>2017-01-18</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>2017-12-19</t>
+          <t>2017-01-26</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>('Email Marketing, Paid Ads, SMS Marketing',)</t>
+          <t>('Photos, Social Media, SEO',)</t>
         </is>
       </c>
     </row>
@@ -4220,47 +4220,47 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1311.2700000000002</t>
+          <t>1981.63</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>8446</t>
+          <t>4935</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>37100</t>
+          <t>22144</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1258.88</t>
+          <t>399.14</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>16109</t>
+          <t>33037</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>52.39</t>
+          <t>1582.49</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2016-06-27</t>
+          <t>2015-09-05</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>2016-08-22</t>
+          <t>2015-09-18</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>('Social Media, Photos, Paid Ads, SMS Marketing, Influencer Marketing',)</t>
+          <t>('Social Media, Photos, Content Marketing, Video, Email Marketing, SMS Marketing',)</t>
         </is>
       </c>
     </row>
@@ -4272,47 +4272,47 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>918.07</t>
+          <t>2205.73</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>5414</t>
+          <t>3986</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>6878</t>
+          <t>23604</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>221.72</t>
+          <t>181.59</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>19283</t>
+          <t>48816</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>696.35</t>
+          <t>2024.14</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2017-07-08</t>
+          <t>2019-06-17</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>2017-08-24</t>
+          <t>2019-06-25</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>('Paid Ads, Email Marketing, SMS Marketing',)</t>
+          <t>('SMS Marketing, Email Marketing, Paid Ads, Video, Influencer Marketing',)</t>
         </is>
       </c>
     </row>
@@ -4324,47 +4324,47 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>930.08</t>
+          <t>2866.71</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>6000</t>
+          <t>1522</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>47654</t>
+          <t>2622</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>834.96</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>60859</t>
+          <t>65623</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>95.12</t>
+          <t>2848.51</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2015-11-16</t>
+          <t>2017-03-19</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2016-01-03</t>
+          <t>2017-04-01</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>('SMS Marketing, Paid Ads, SEO, Email Marketing, Influencer Marketing',)</t>
+          <t>('Video, Social Media, Influencer Marketing, SMS Marketing',)</t>
         </is>
       </c>
     </row>
@@ -4376,47 +4376,47 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>412.74</t>
+          <t>1455.65</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>6464</t>
+          <t>8386</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>11302</t>
+          <t>46788</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>275.42</t>
+          <t>1145.25</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>16448</t>
+          <t>8644</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>137.32</t>
+          <t>310.4</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2018-10-30</t>
+          <t>2015-11-27</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>2018-12-16</t>
+          <t>2015-12-03</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>('Paid Ads, Content Marketing, Influencer Marketing, Email Marketing',)</t>
+          <t>('SMS Marketing, Photos, Paid Ads, Social Media',)</t>
         </is>
       </c>
     </row>
@@ -4428,47 +4428,47 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>4228.18</t>
+          <t>1379.76</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>5421</t>
+          <t>9624</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>35763</t>
+          <t>36791</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1342.97</t>
+          <t>1099.57</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>74390</t>
+          <t>7079</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2885.21</t>
+          <t>280.19</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2018-11-03</t>
+          <t>2015-06-10</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>2018-12-20</t>
+          <t>2015-06-19</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>('Influencer Marketing, Photos, Social Media, Paid Ads, SEO',)</t>
+          <t>('SMS Marketing, Influencer Marketing, Social Media, Photos, SEO',)</t>
         </is>
       </c>
     </row>
@@ -4480,47 +4480,47 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1541.91</t>
+          <t>1309.1</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>7617</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>29110</t>
+          <t>47177</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>211.76</t>
+          <t>1308.84</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>47169</t>
+          <t>1582</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>1330.15</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2016-09-22</t>
+          <t>2018-03-25</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>2016-11-11</t>
+          <t>2018-04-05</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>('SEO, Content Marketing, Photos',)</t>
+          <t>('Social Media, Photos, Influencer Marketing, Email Marketing',)</t>
         </is>
       </c>
     </row>
@@ -4532,47 +4532,47 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>1590.54</t>
+          <t>1316.74</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>6618</t>
+          <t>8850</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>6393</t>
+          <t>9437</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>221.08</t>
+          <t>325.99</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>74719</t>
+          <t>60994</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>1369.46</t>
+          <t>990.75</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2019-01-19</t>
+          <t>2015-10-08</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>2019-03-09</t>
+          <t>2015-10-20</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>('Influencer Marketing, Email Marketing, Video, Paid Ads, Social Media, Content Marketing',)</t>
+          <t>('Social Media, SEO, SMS Marketing, Photos, Video, Content Marketing',)</t>
         </is>
       </c>
     </row>
@@ -4584,47 +4584,47 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>470.84999999999997</t>
+          <t>1479.6200000000001</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>7858</t>
+          <t>6016</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>31775</t>
+          <t>2568</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>433.52</t>
+          <t>51.21</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>5387</t>
+          <t>29562</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>37.33</t>
+          <t>1428.41</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2017-03-26</t>
+          <t>2018-05-02</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>2017-05-15</t>
+          <t>2018-05-08</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>('Paid Ads, Content Marketing, Photos, Influencer Marketing, Email Marketing',)</t>
+          <t>('Social Media, SEO, Video, Content Marketing, SMS Marketing',)</t>
         </is>
       </c>
     </row>
@@ -4636,47 +4636,47 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>850.12</t>
+          <t>4014.64</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>1872</t>
+          <t>3400</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>29727</t>
+          <t>33127</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>743.57</t>
+          <t>1620.5</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>23861</t>
+          <t>61429</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>106.55</t>
+          <t>2394.14</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2019-01-30</t>
+          <t>2018-12-13</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>2019-03-24</t>
+          <t>2018-12-24</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>('Content Marketing, Photos, Video, Email Marketing, Social Media',)</t>
+          <t>('SMS Marketing, Photos, Paid Ads, Email Marketing, Influencer Marketing',)</t>
         </is>
       </c>
     </row>
@@ -4688,47 +4688,47 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>1464.6599999999999</t>
+          <t>839.3199999999999</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2703</t>
+          <t>7105</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>32830</t>
+          <t>13645</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>1108.79</t>
+          <t>86.67</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>12740</t>
+          <t>45513</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>355.87</t>
+          <t>752.65</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2016-08-17</t>
+          <t>2019-02-16</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>2016-10-08</t>
+          <t>2019-02-27</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>('SMS Marketing, SEO, Content Marketing',)</t>
+          <t>('Video, Email Marketing, Paid Ads, SEO',)</t>
         </is>
       </c>
     </row>
@@ -4740,47 +4740,47 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2018.85</t>
+          <t>879.21</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>7362</t>
+          <t>4287</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>3828</t>
+          <t>38798</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>38.61</t>
+          <t>223.14</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>47416</t>
+          <t>27283</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>1980.24</t>
+          <t>656.07</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2018-11-10</t>
+          <t>2016-03-14</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>2019-01-02</t>
+          <t>2016-03-23</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>('Photos, SMS Marketing, Paid Ads, Content Marketing, Social Media',)</t>
+          <t>('Email Marketing, Paid Ads, SMS Marketing',)</t>
         </is>
       </c>
     </row>
@@ -4792,47 +4792,47 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2433.5200000000004</t>
+          <t>1311.2700000000002</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>7877</t>
+          <t>8446</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>31707</t>
+          <t>37100</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>1081.39</t>
+          <t>1258.88</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>30282</t>
+          <t>16109</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>1352.13</t>
+          <t>52.39</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2016-05-12</t>
+          <t>2016-03-14</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>2016-07-05</t>
+          <t>2016-03-29</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>('Email Marketing, Content Marketing, Paid Ads',)</t>
+          <t>('Social Media, Photos, Paid Ads, SMS Marketing, Influencer Marketing',)</t>
         </is>
       </c>
     </row>
@@ -4844,47 +4844,47 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1819.1699999999998</t>
+          <t>686.8299999999999</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>5128</t>
+          <t>4819</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>3757</t>
+          <t>23741</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>77.81</t>
+          <t>386.65</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>37467</t>
+          <t>23641</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>1741.36</t>
+          <t>300.18</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2016-10-27</t>
+          <t>2015-07-01</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>2016-12-20</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>('Influencer Marketing, Photos, Social Media, Paid Ads, Video, SMS Marketing',)</t>
+          <t>('Paid Ads, Email Marketing, SMS Marketing',)</t>
         </is>
       </c>
     </row>
@@ -4896,47 +4896,47 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2114.45</t>
+          <t>930.08</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>6308</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>32237</t>
+          <t>47654</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>859.24</t>
+          <t>834.96</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>37828</t>
+          <t>60859</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>1255.21</t>
+          <t>95.12</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2019-11-08</t>
+          <t>2015-12-21</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>2019-12-29</t>
+          <t>2015-12-28</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>('Social Media, SEO, Photos',)</t>
+          <t>('SMS Marketing, Paid Ads, SEO, Email Marketing, Influencer Marketing',)</t>
         </is>
       </c>
     </row>
@@ -4948,47 +4948,47 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2034.3700000000001</t>
+          <t>801.11</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>1437</t>
+          <t>7793</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>26978</t>
+          <t>30751</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>776.44</t>
+          <t>444.7</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>45954</t>
+          <t>32288</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>1257.93</t>
+          <t>356.41</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2018-06-12</t>
+          <t>2016-04-15</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>2018-07-30</t>
+          <t>2016-04-23</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>('Content Marketing, SMS Marketing, Photos, Social Media, Email Marketing, Influencer Marketing',)</t>
+          <t>('Paid Ads, Content Marketing, Influencer Marketing, Email Marketing',)</t>
         </is>
       </c>
     </row>
@@ -5000,47 +5000,47 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>619.1500000000001</t>
+          <t>4228.18</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>1013</t>
+          <t>5421</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>28538</t>
+          <t>35763</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>166.74</t>
+          <t>1342.97</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>10383</t>
+          <t>74390</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>452.41</t>
+          <t>2885.21</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2017-12-26</t>
+          <t>2016-01-10</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>2018-02-15</t>
+          <t>2016-01-16</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>('Email Marketing, Photos, Content Marketing, Video, Paid Ads',)</t>
+          <t>('Influencer Marketing, Photos, Social Media, Paid Ads, SEO',)</t>
         </is>
       </c>
     </row>
@@ -5052,47 +5052,47 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>923.86</t>
+          <t>1541.91</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>9064</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>11280</t>
+          <t>29110</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>421.73</t>
+          <t>211.76</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>44729</t>
+          <t>47169</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>502.13</t>
+          <t>1330.15</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2018-08-29</t>
+          <t>2018-06-12</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>2018-10-17</t>
+          <t>2018-06-21</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>('Influencer Marketing, Social Media, SMS Marketing',)</t>
+          <t>('SEO, Content Marketing, Photos',)</t>
         </is>
       </c>
     </row>
@@ -5104,47 +5104,47 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2659.38</t>
+          <t>1590.54</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>7754</t>
+          <t>6618</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>44268</t>
+          <t>6393</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>1769.22</t>
+          <t>221.08</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>33936</t>
+          <t>74719</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>890.16</t>
+          <t>1369.46</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2017-03-27</t>
+          <t>2015-10-20</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>2017-05-16</t>
+          <t>2015-10-28</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>('SMS Marketing, SEO, Email Marketing, Paid Ads, Social Media',)</t>
+          <t>('Influencer Marketing, Email Marketing, Video, Paid Ads, Social Media, Content Marketing',)</t>
         </is>
       </c>
     </row>
@@ -5156,47 +5156,47 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2089.14</t>
+          <t>470.84999999999997</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>9358</t>
+          <t>7858</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>1699</t>
+          <t>31775</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>72.77</t>
+          <t>433.52</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>53540</t>
+          <t>5387</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2016.37</t>
+          <t>37.33</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2018-04-30</t>
+          <t>2017-05-26</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>2018-06-18</t>
+          <t>2017-06-04</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>('Social Media, Paid Ads, Photos, Influencer Marketing',)</t>
+          <t>('Paid Ads, Content Marketing, Photos, Influencer Marketing, Email Marketing',)</t>
         </is>
       </c>
     </row>
@@ -5208,47 +5208,47 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>1148.26</t>
+          <t>850.12</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>5523</t>
+          <t>1872</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>25806</t>
+          <t>29727</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>810.99</t>
+          <t>743.57</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>13880</t>
+          <t>23861</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>337.27</t>
+          <t>106.55</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2016-06-05</t>
+          <t>2015-09-14</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>2016-07-27</t>
+          <t>2015-09-26</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>('Social Media, Photos, Influencer Marketing, Video, SEO, Content Marketing',)</t>
+          <t>('Content Marketing, Photos, Video, Email Marketing, Social Media',)</t>
         </is>
       </c>
     </row>
@@ -5260,47 +5260,47 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>380.44</t>
+          <t>1464.6599999999999</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>2703</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>11283</t>
+          <t>32830</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>238.74</t>
+          <t>1108.79</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>7499</t>
+          <t>12740</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>141.7</t>
+          <t>355.87</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2016-02-12</t>
+          <t>2019-11-29</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>2016-04-03</t>
+          <t>2019-12-10</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>('Email Marketing, Paid Ads, SEO, Social Media',)</t>
+          <t>('SMS Marketing, SEO, Content Marketing',)</t>
         </is>
       </c>
     </row>
@@ -5312,47 +5312,47 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1037.24</t>
+          <t>539.29</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2601</t>
+          <t>6969</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>34705</t>
+          <t>35637</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>603.98</t>
+          <t>270.72</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>50731</t>
+          <t>8487</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>433.26</t>
+          <t>268.57</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2019-08-13</t>
+          <t>2019-12-11</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>2019-10-01</t>
+          <t>2019-12-24</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>('Photos, Influencer Marketing, Video',)</t>
+          <t>('Photos, SMS Marketing, Paid Ads, Content Marketing, Social Media',)</t>
         </is>
       </c>
     </row>
@@ -5364,47 +5364,47 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>1483.3899999999999</t>
+          <t>2433.5200000000004</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>9336</t>
+          <t>7877</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>29870</t>
+          <t>31707</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>590.51</t>
+          <t>1081.39</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>36134</t>
+          <t>30282</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>892.88</t>
+          <t>1352.13</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2019-03-04</t>
+          <t>2015-11-07</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>2019-04-23</t>
+          <t>2015-11-20</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>('Content Marketing, SMS Marketing, Photos',)</t>
+          <t>('Email Marketing, Content Marketing, Paid Ads',)</t>
         </is>
       </c>
     </row>
@@ -5416,47 +5416,47 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2792.79</t>
+          <t>1167.52</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>8708</t>
+          <t>4819</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>36996</t>
+          <t>39647</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>1849.57</t>
+          <t>737.55</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>25338</t>
+          <t>60668</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>943.22</t>
+          <t>429.97</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2015-12-11</t>
+          <t>2016-11-05</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>2016-02-02</t>
+          <t>2016-11-13</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>('SEO, Paid Ads, Social Media, Video, Email Marketing, Content Marketing',)</t>
+          <t>('Email Marketing, Photos, Paid Ads, SMS Marketing',)</t>
         </is>
       </c>
     </row>
@@ -5468,47 +5468,47 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>1847.29</t>
+          <t>2870.98</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>3966</t>
+          <t>3132</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>30734</t>
+          <t>27815</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>830.25</t>
+          <t>965.58</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>33357</t>
+          <t>64529</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>1017.04</t>
+          <t>1905.4</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2016-12-30</t>
+          <t>2017-07-30</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>2017-02-18</t>
+          <t>2017-08-05</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>('SEO, Social Media, SMS Marketing',)</t>
+          <t>('SEO, Video, SMS Marketing, Content Marketing, Influencer Marketing',)</t>
         </is>
       </c>
     </row>
@@ -5520,47 +5520,47 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>1786.13</t>
+          <t>1121.0700000000002</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>8829</t>
+          <t>3806</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>46258</t>
+          <t>9526</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>1566.88</t>
+          <t>68.44</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>10408</t>
+          <t>39767</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>219.25</t>
+          <t>1052.63</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2017-12-10</t>
+          <t>2018-06-08</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>2018-02-01</t>
+          <t>2018-06-13</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>('Social Media, Photos, Video, Paid Ads, Influencer Marketing',)</t>
+          <t>('Influencer Marketing, Content Marketing, SEO, Social Media, Photos, Paid Ads',)</t>
         </is>
       </c>
     </row>
@@ -5572,47 +5572,47 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2856.77</t>
+          <t>546.23</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>3968</t>
+          <t>9778</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>18397</t>
+          <t>24610</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>301.17</t>
+          <t>277.88</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>68146</t>
+          <t>6313</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2555.6</t>
+          <t>268.35</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2019-10-25</t>
+          <t>2016-06-19</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>2019-12-16</t>
+          <t>2016-07-03</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>('Influencer Marketing, Email Marketing, SMS Marketing, Content Marketing, Paid Ads, Video',)</t>
+          <t>('Content Marketing, SEO, SMS Marketing',)</t>
         </is>
       </c>
     </row>
@@ -5624,47 +5624,47 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>1542.1100000000001</t>
+          <t>5413.92</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2929</t>
+          <t>2596</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>48571</t>
+          <t>39455</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>1005.42</t>
+          <t>1893.63</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>60063</t>
+          <t>73985</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>536.69</t>
+          <t>3520.29</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2017-05-12</t>
+          <t>2019-07-11</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>2017-07-01</t>
+          <t>2019-07-19</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>('Photos, Content Marketing, Paid Ads, Email Marketing',)</t>
+          <t>('Email Marketing, Influencer Marketing, Content Marketing, Video, SEO, Photos',)</t>
         </is>
       </c>
     </row>
